--- a/users.xlsx
+++ b/users.xlsx
@@ -26,7 +26,7 @@
     <t>User1</t>
   </si>
   <si>
-    <t>user1@example.com</t>
+    <t>user1@gmail.com</t>
   </si>
   <si>
     <t>19</t>
@@ -44,7 +44,7 @@
     <t>User3</t>
   </si>
   <si>
-    <t>user3n@hotmail.com</t>
+    <t>user3@gmail.com</t>
   </si>
   <si>
     <t>24</t>
